--- a/Template_Horarios_Grupos_Vespertino_5.xlsx
+++ b/Template_Horarios_Grupos_Vespertino_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\source\repos\CBTis73\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33C66E1-484F-42D3-B599-A163EE0B80ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33107815-DD54-407F-8426-8071B94973F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,13 +507,28 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -522,54 +537,42 @@
     <xf numFmtId="20" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="11" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -579,26 +582,23 @@
     <xf numFmtId="20" fontId="23" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1345,12 +1345,12 @@
       <c r="A1" s="13"/>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2"/>
     </row>
@@ -1358,12 +1358,12 @@
       <c r="A2" s="13"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="4"/>
       <c r="I2" s="5"/>
       <c r="J2">
@@ -1393,12 +1393,12 @@
       <c r="A4" s="13"/>
       <c r="B4" s="12"/>
       <c r="C4" s="18"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="60" t="s">
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="60"/>
+      <c r="G4" s="53"/>
       <c r="H4" s="6"/>
       <c r="I4" s="5"/>
       <c r="J4">
@@ -1429,15 +1429,15 @@
       <c r="B6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="62"/>
-      <c r="E6" s="63" t="s">
+      <c r="D6" s="51"/>
+      <c r="E6" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
       <c r="H6" s="7"/>
       <c r="I6" s="5"/>
       <c r="J6">
@@ -1497,14 +1497,14 @@
     </row>
     <row r="9" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15"/>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="9"/>
       <c r="I9" s="5"/>
       <c r="J9">
@@ -1520,12 +1520,12 @@
     </row>
     <row r="10" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="9"/>
       <c r="I10" s="5"/>
       <c r="J10">
@@ -1544,11 +1544,11 @@
       <c r="B11" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="9"/>
       <c r="I11" s="5"/>
       <c r="J11">
@@ -1565,11 +1565,11 @@
     <row r="12" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15"/>
       <c r="B12" s="39"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="H12" s="9"/>
       <c r="I12" s="5"/>
       <c r="J12">
@@ -1585,14 +1585,14 @@
     </row>
     <row r="13" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="15"/>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="9"/>
       <c r="I13" s="5"/>
       <c r="J13">
@@ -1608,12 +1608,12 @@
     </row>
     <row r="14" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="15"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
       <c r="H14" s="9"/>
       <c r="I14" s="5"/>
       <c r="J14">
@@ -1655,13 +1655,13 @@
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="57"/>
       <c r="H16" s="9"/>
       <c r="I16" s="5"/>
       <c r="J16">
@@ -1680,11 +1680,11 @@
       <c r="B17" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="9"/>
       <c r="I17" s="5"/>
       <c r="J17">
@@ -1701,11 +1701,11 @@
     <row r="18" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="15"/>
       <c r="B18" s="39"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
       <c r="H18" s="9"/>
       <c r="I18" s="5"/>
       <c r="J18">
@@ -1724,11 +1724,11 @@
       <c r="B19" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="9"/>
       <c r="I19" s="5"/>
       <c r="J19">
@@ -1745,11 +1745,11 @@
     <row r="20" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="15"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
       <c r="H20" s="9"/>
       <c r="I20" s="5"/>
       <c r="J20">
@@ -1768,11 +1768,11 @@
       <c r="B21" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="9"/>
       <c r="I21" s="5"/>
       <c r="J21">
@@ -1789,11 +1789,11 @@
     <row r="22" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="15"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="9"/>
       <c r="I22" s="5"/>
       <c r="J22">
@@ -1812,11 +1812,11 @@
       <c r="B23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="36"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="41"/>
       <c r="H23" s="9"/>
       <c r="I23" s="5"/>
       <c r="J23">
@@ -1833,11 +1833,11 @@
     <row r="24" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="15"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="37"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="9"/>
       <c r="I24" s="5"/>
       <c r="J24">
@@ -1880,12 +1880,12 @@
       <c r="C26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="49"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="37"/>
       <c r="H26" s="9"/>
       <c r="I26" s="5"/>
       <c r="J26">
@@ -1907,10 +1907,10 @@
       <c r="C27" s="25">
         <v>5</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="60"/>
       <c r="H27" s="9"/>
       <c r="I27" s="5"/>
       <c r="J27">
@@ -1932,10 +1932,10 @@
       <c r="C28" s="25">
         <v>5</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="60"/>
       <c r="H28" s="9"/>
       <c r="I28" s="5"/>
       <c r="J28">
@@ -1957,10 +1957,10 @@
       <c r="C29" s="25">
         <v>4</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="60"/>
       <c r="H29" s="9"/>
       <c r="I29" s="5"/>
       <c r="J29">
@@ -1982,10 +1982,10 @@
       <c r="C30" s="25">
         <v>3</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="60"/>
       <c r="H30" s="9"/>
       <c r="I30" s="5"/>
       <c r="J30">
@@ -2003,10 +2003,10 @@
       <c r="C31" s="25">
         <v>1</v>
       </c>
-      <c r="D31" s="44"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="46"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="60"/>
       <c r="H31" s="9"/>
       <c r="I31" s="5"/>
       <c r="J31">
@@ -2024,10 +2024,10 @@
       <c r="C32" s="25">
         <v>3</v>
       </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="46"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="60"/>
       <c r="H32" s="9"/>
       <c r="I32" s="5"/>
       <c r="J32">
@@ -2045,10 +2045,10 @@
       <c r="C33" s="25">
         <v>7</v>
       </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="46"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="60"/>
       <c r="H33" s="9"/>
       <c r="I33" s="5"/>
       <c r="J33">
@@ -2066,10 +2066,10 @@
       <c r="C34" s="25">
         <v>5</v>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="46"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="60"/>
       <c r="H34" s="9"/>
       <c r="I34" s="5"/>
     </row>
@@ -2081,10 +2081,10 @@
       <c r="C35" s="25">
         <v>1</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="46"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="60"/>
       <c r="H35" s="9"/>
       <c r="I35" s="5"/>
     </row>
@@ -2104,13 +2104,13 @@
       <c r="B37" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="47" t="s">
+      <c r="C37" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="49"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="37"/>
       <c r="H37" s="9"/>
       <c r="I37" s="5"/>
       <c r="J37">
@@ -2123,11 +2123,11 @@
     <row r="38" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A38" s="13"/>
       <c r="B38" s="25"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="46"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="60"/>
       <c r="H38" s="9"/>
       <c r="I38" s="5"/>
       <c r="J38">
@@ -2140,11 +2140,11 @@
     <row r="39" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A39" s="13"/>
       <c r="B39" s="25"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="35"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="63"/>
       <c r="I39" s="5"/>
       <c r="J39">
         <v>39</v>
@@ -2156,21 +2156,21 @@
     <row r="40" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A40" s="13"/>
       <c r="B40" s="25"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="35"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="63"/>
       <c r="I40" s="5"/>
     </row>
     <row r="41" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A41" s="13"/>
       <c r="B41" s="25"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="35"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="62"/>
+      <c r="G41" s="63"/>
       <c r="I41" s="5"/>
       <c r="J41">
         <v>40</v>
@@ -2182,11 +2182,11 @@
     <row r="42" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A42" s="13"/>
       <c r="B42" s="25"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="35"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="63"/>
       <c r="I42" s="5"/>
       <c r="J42">
         <v>41</v>
@@ -2198,11 +2198,11 @@
     <row r="43" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A43" s="13"/>
       <c r="B43" s="25"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="35"/>
+      <c r="C43" s="61"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="63"/>
       <c r="I43" s="5"/>
       <c r="J43">
         <v>42</v>
@@ -2214,11 +2214,11 @@
     <row r="44" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A44" s="13"/>
       <c r="B44" s="25"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="35"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="63"/>
       <c r="I44" s="5"/>
       <c r="J44">
         <v>43</v>
@@ -2230,11 +2230,11 @@
     <row r="45" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A45" s="13"/>
       <c r="B45" s="25"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="46"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="60"/>
       <c r="I45" s="5"/>
       <c r="J45">
         <v>44</v>
@@ -2246,11 +2246,11 @@
     <row r="46" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A46" s="13"/>
       <c r="B46" s="25"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="46"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="60"/>
       <c r="H46" s="8"/>
       <c r="I46" s="5"/>
       <c r="J46">
@@ -2290,16 +2290,16 @@
     </row>
     <row r="49" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A49" s="13"/>
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="42"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42" t="s">
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="42"/>
-      <c r="G49" s="42"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
       <c r="H49" s="8"/>
       <c r="I49" s="5"/>
       <c r="J49">
@@ -2311,16 +2311,16 @@
     </row>
     <row r="50" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A50" s="13"/>
-      <c r="B50" s="43" t="s">
+      <c r="B50" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43" t="s">
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
       <c r="H50" s="8"/>
       <c r="I50" s="5"/>
       <c r="J50">
@@ -2362,46 +2362,46 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B53" s="42" t="s">
+      <c r="B53" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42" t="s">
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B54" s="43" t="s">
+      <c r="B54" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43" t="s">
+      <c r="C54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
-      <c r="D55" s="41" t="s">
+      <c r="D55" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B56" s="29"/>
       <c r="C56" s="29"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
       <c r="L56" s="11"/>
     </row>
     <row r="57" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
@@ -2427,48 +2427,21 @@
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="G13:G14"/>
@@ -2485,21 +2458,48 @@
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="D32:G32"/>
     <mergeCell ref="D33:G33"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="C45:G45"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup scale="89" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/Template_Horarios_Grupos_Vespertino_5.xlsx
+++ b/Template_Horarios_Grupos_Vespertino_5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\source\repos\CBTis73\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33107815-DD54-407F-8426-8071B94973F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C740CF44-0336-4A96-892C-A5013A2DA463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="GRUPO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">GRUPO!$A$1:$H$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">GRUPO!$A$1:$H$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -507,98 +507,98 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="20" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="23" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="23" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="20" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="23" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="23" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -677,13 +677,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>296333</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>772583</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -727,13 +727,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>214578</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>239713</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>833703</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>8202</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -777,13 +777,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>148167</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -827,13 +827,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>71438</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>226219</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>750094</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -877,13 +877,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>80964</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>842963</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>211931</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -927,13 +927,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>148167</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -977,13 +977,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>148167</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1327,7 +1327,7 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="16.3984375" customWidth="1"/>
@@ -1345,12 +1345,12 @@
       <c r="A1" s="13"/>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2"/>
     </row>
@@ -1358,12 +1358,12 @@
       <c r="A2" s="13"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="4"/>
       <c r="I2" s="5"/>
       <c r="J2">
@@ -1393,12 +1393,12 @@
       <c r="A4" s="13"/>
       <c r="B4" s="12"/>
       <c r="C4" s="18"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="53" t="s">
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="53"/>
+      <c r="G4" s="55"/>
       <c r="H4" s="6"/>
       <c r="I4" s="5"/>
       <c r="J4">
@@ -1429,15 +1429,15 @@
       <c r="B6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="52" t="s">
+      <c r="D6" s="53"/>
+      <c r="E6" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
       <c r="H6" s="7"/>
       <c r="I6" s="5"/>
       <c r="J6">
@@ -1497,14 +1497,14 @@
     </row>
     <row r="9" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15"/>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
       <c r="H9" s="9"/>
       <c r="I9" s="5"/>
       <c r="J9">
@@ -1520,12 +1520,12 @@
     </row>
     <row r="10" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
       <c r="H10" s="9"/>
       <c r="I10" s="5"/>
       <c r="J10">
@@ -1541,14 +1541,14 @@
     </row>
     <row r="11" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="15"/>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="9"/>
       <c r="I11" s="5"/>
       <c r="J11">
@@ -1564,12 +1564,12 @@
     </row>
     <row r="12" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
       <c r="H12" s="9"/>
       <c r="I12" s="5"/>
       <c r="J12">
@@ -1585,14 +1585,14 @@
     </row>
     <row r="13" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="15"/>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
       <c r="H13" s="9"/>
       <c r="I13" s="5"/>
       <c r="J13">
@@ -1608,12 +1608,12 @@
     </row>
     <row r="14" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="15"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
       <c r="H14" s="9"/>
       <c r="I14" s="5"/>
       <c r="J14">
@@ -1655,13 +1655,13 @@
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="57"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="45"/>
       <c r="H16" s="9"/>
       <c r="I16" s="5"/>
       <c r="J16">
@@ -1677,14 +1677,14 @@
     </row>
     <row r="17" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="15"/>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="9"/>
       <c r="I17" s="5"/>
       <c r="J17">
@@ -1700,12 +1700,12 @@
     </row>
     <row r="18" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="15"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="9"/>
       <c r="I18" s="5"/>
       <c r="J18">
@@ -1721,14 +1721,14 @@
     </row>
     <row r="19" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="15"/>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
       <c r="H19" s="9"/>
       <c r="I19" s="5"/>
       <c r="J19">
@@ -1744,12 +1744,12 @@
     </row>
     <row r="20" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="15"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
       <c r="H20" s="9"/>
       <c r="I20" s="5"/>
       <c r="J20">
@@ -1765,14 +1765,14 @@
     </row>
     <row r="21" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="15"/>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
       <c r="H21" s="9"/>
       <c r="I21" s="5"/>
       <c r="J21">
@@ -1788,12 +1788,12 @@
     </row>
     <row r="22" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="15"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
       <c r="H22" s="9"/>
       <c r="I22" s="5"/>
       <c r="J22">
@@ -1809,14 +1809,14 @@
     </row>
     <row r="23" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="15"/>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="41"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="38"/>
       <c r="H23" s="9"/>
       <c r="I23" s="5"/>
       <c r="J23">
@@ -1832,12 +1832,12 @@
     </row>
     <row r="24" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="15"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="42"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="39"/>
       <c r="H24" s="9"/>
       <c r="I24" s="5"/>
       <c r="J24">
@@ -1880,12 +1880,12 @@
       <c r="C26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="37"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58"/>
       <c r="H26" s="9"/>
       <c r="I26" s="5"/>
       <c r="J26">
@@ -1907,10 +1907,10 @@
       <c r="C27" s="25">
         <v>5</v>
       </c>
-      <c r="D27" s="58"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="60"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="48"/>
       <c r="H27" s="9"/>
       <c r="I27" s="5"/>
       <c r="J27">
@@ -1932,10 +1932,10 @@
       <c r="C28" s="25">
         <v>5</v>
       </c>
-      <c r="D28" s="58"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="60"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="48"/>
       <c r="H28" s="9"/>
       <c r="I28" s="5"/>
       <c r="J28">
@@ -1957,10 +1957,10 @@
       <c r="C29" s="25">
         <v>4</v>
       </c>
-      <c r="D29" s="58"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="60"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="48"/>
       <c r="H29" s="9"/>
       <c r="I29" s="5"/>
       <c r="J29">
@@ -1982,10 +1982,10 @@
       <c r="C30" s="25">
         <v>3</v>
       </c>
-      <c r="D30" s="58"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="60"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="48"/>
       <c r="H30" s="9"/>
       <c r="I30" s="5"/>
       <c r="J30">
@@ -2003,10 +2003,10 @@
       <c r="C31" s="25">
         <v>1</v>
       </c>
-      <c r="D31" s="58"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="60"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="48"/>
       <c r="H31" s="9"/>
       <c r="I31" s="5"/>
       <c r="J31">
@@ -2024,10 +2024,10 @@
       <c r="C32" s="25">
         <v>3</v>
       </c>
-      <c r="D32" s="58"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="60"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48"/>
       <c r="H32" s="9"/>
       <c r="I32" s="5"/>
       <c r="J32">
@@ -2045,10 +2045,10 @@
       <c r="C33" s="25">
         <v>7</v>
       </c>
-      <c r="D33" s="58"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="60"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="48"/>
       <c r="H33" s="9"/>
       <c r="I33" s="5"/>
       <c r="J33">
@@ -2060,78 +2060,72 @@
     </row>
     <row r="34" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="13"/>
-      <c r="B34" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="25">
-        <v>5</v>
-      </c>
-      <c r="D34" s="58"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="60"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="9"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="13"/>
       <c r="B35" s="25" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C35" s="25">
-        <v>1</v>
-      </c>
-      <c r="D35" s="58"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="60"/>
+        <v>5</v>
+      </c>
+      <c r="D35" s="46"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="48"/>
       <c r="H35" s="9"/>
       <c r="I35" s="5"/>
     </row>
-    <row r="36" spans="1:12" ht="18" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="13"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
+      <c r="B36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="25">
+        <v>1</v>
+      </c>
+      <c r="D36" s="46"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="48"/>
       <c r="H36" s="9"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A37" s="13"/>
-      <c r="B37" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="37"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
       <c r="H37" s="9"/>
       <c r="I37" s="5"/>
-      <c r="J37">
-        <v>36</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="38" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A38" s="13"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="60"/>
+      <c r="B38" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="58"/>
       <c r="H38" s="9"/>
       <c r="I38" s="5"/>
       <c r="J38">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>2</v>
@@ -2140,14 +2134,15 @@
     <row r="39" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A39" s="13"/>
       <c r="B39" s="25"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="63"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="9"/>
       <c r="I39" s="5"/>
       <c r="J39">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>2</v>
@@ -2156,40 +2151,40 @@
     <row r="40" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A40" s="13"/>
       <c r="B40" s="25"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="62"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="63"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="35"/>
       <c r="I40" s="5"/>
+      <c r="J40">
+        <v>39</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A41" s="13"/>
       <c r="B41" s="25"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="62"/>
-      <c r="G41" s="63"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="35"/>
       <c r="I41" s="5"/>
-      <c r="J41">
-        <v>40</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="42" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A42" s="13"/>
       <c r="B42" s="25"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="63"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="35"/>
       <c r="I42" s="5"/>
       <c r="J42">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>2</v>
@@ -2198,14 +2193,14 @@
     <row r="43" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A43" s="13"/>
       <c r="B43" s="25"/>
-      <c r="C43" s="61"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="63"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="35"/>
       <c r="I43" s="5"/>
       <c r="J43">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>2</v>
@@ -2214,14 +2209,14 @@
     <row r="44" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A44" s="13"/>
       <c r="B44" s="25"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="62"/>
-      <c r="E44" s="62"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="63"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="35"/>
       <c r="I44" s="5"/>
       <c r="J44">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>2</v>
@@ -2230,14 +2225,14 @@
     <row r="45" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A45" s="13"/>
       <c r="B45" s="25"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="60"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="35"/>
       <c r="I45" s="5"/>
       <c r="J45">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>2</v>
@@ -2246,32 +2241,24 @@
     <row r="46" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A46" s="13"/>
       <c r="B46" s="25"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="60"/>
-      <c r="H46" s="8"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="35"/>
       <c r="I46" s="5"/>
-      <c r="J46">
-        <v>45</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="47" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A47" s="13"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="8"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="48"/>
       <c r="I47" s="5"/>
       <c r="J47">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>2</v>
@@ -2279,31 +2266,33 @@
     </row>
     <row r="48" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A48" s="13"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="48"/>
       <c r="H48" s="8"/>
       <c r="I48" s="5"/>
+      <c r="J48">
+        <v>45</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A49" s="13"/>
-      <c r="B49" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
       <c r="H49" s="8"/>
       <c r="I49" s="5"/>
       <c r="J49">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>2</v>
@@ -2311,169 +2300,168 @@
     </row>
     <row r="50" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A50" s="13"/>
-      <c r="B50" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
       <c r="H50" s="8"/>
       <c r="I50" s="5"/>
-      <c r="J50">
-        <v>48</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="51" spans="1:12" ht="18" x14ac:dyDescent="0.45">
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="62" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" s="62"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="62" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51" s="62"/>
+      <c r="G51" s="62"/>
       <c r="H51" s="8"/>
       <c r="I51" s="5"/>
       <c r="J51">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="18" x14ac:dyDescent="0.45">
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="8"/>
       <c r="I52" s="5"/>
       <c r="J52">
+        <v>48</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="18" x14ac:dyDescent="0.45">
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="5"/>
+      <c r="J53">
+        <v>49</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="18" x14ac:dyDescent="0.45">
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="I54" s="5"/>
+      <c r="J54">
         <v>50</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B53" s="34" t="s">
+      <c r="L54" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B55" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34" t="s">
+      <c r="C55" s="62"/>
+      <c r="D55" s="62"/>
+      <c r="E55" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B54" s="33" t="s">
+      <c r="F55" s="62"/>
+      <c r="G55" s="62"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B56" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33" t="s">
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="54" t="s">
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="L56" s="11"/>
-    </row>
-    <row r="57" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="L57" s="11"/>
-    </row>
-    <row r="58" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
       <c r="L58" s="11"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
       <c r="L59" s="11"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
       <c r="L60" s="11"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L61" s="11"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L62" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="D56:G56"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="E55:G55"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="D26:G26"/>
@@ -2486,20 +2474,53 @@
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="F23:F24"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="D58:G58"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup scale="89" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
